--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cobertura APS de vejez</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="710">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Aysen</t>
@@ -181,6 +181,12 @@
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maule</t>
   </si>
   <si>
@@ -190,12 +196,6 @@
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">5702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">7304</t>
   </si>
   <si>
@@ -220,21 +220,21 @@
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
+    <t xml:space="preserve">Metropolitana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
     <t xml:space="preserve">7307</t>
   </si>
   <si>
     <t xml:space="preserve">Sagrada Familia</t>
   </si>
   <si>
-    <t xml:space="preserve">Metropolitana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
     <t xml:space="preserve">7308</t>
   </si>
   <si>
@@ -799,18 +799,18 @@
     <t xml:space="preserve">La Cruz</t>
   </si>
   <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">7303</t>
   </si>
   <si>
     <t xml:space="preserve">Licantén</t>
   </si>
   <si>
-    <t xml:space="preserve">5401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
     <t xml:space="preserve">13102</t>
   </si>
   <si>
@@ -967,18 +967,18 @@
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
+    <t xml:space="preserve">5405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
     <t xml:space="preserve">7106</t>
   </si>
   <si>
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
-    <t xml:space="preserve">5405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
     <t xml:space="preserve">13503</t>
   </si>
   <si>
@@ -1699,18 +1699,18 @@
     <t xml:space="preserve">Chiguayante</t>
   </si>
   <si>
+    <t xml:space="preserve">14106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
     <t xml:space="preserve">10404</t>
   </si>
   <si>
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">14106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
     <t xml:space="preserve">8310</t>
   </si>
   <si>
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:28</t>
+    <t xml:space="preserve">2026-07-30 15:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2113,16 +2113,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_p_aps_a_2019.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura APS de vejez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -3127,16 +3136,16 @@
         <v>2019</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>48</v>
@@ -3159,10 +3168,10 @@
         <v>2019</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>57</v>
@@ -3194,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>59</v>
@@ -3319,16 +3328,16 @@
         <v>2019</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>48</v>
@@ -3351,10 +3360,10 @@
         <v>2019</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>70</v>
@@ -3386,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>72</v>
@@ -3418,7 +3427,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>74</v>
@@ -3514,7 +3523,7 @@
         <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>80</v>
@@ -3674,7 +3683,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>90</v>
@@ -3866,7 +3875,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3930,7 +3939,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -3962,7 +3971,7 @@
         <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -4058,7 +4067,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4122,7 +4131,7 @@
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4250,7 +4259,7 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4282,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4378,7 +4387,7 @@
         <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4410,7 +4419,7 @@
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4666,7 +4675,7 @@
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>153</v>
@@ -4698,7 +4707,7 @@
         <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4730,7 +4739,7 @@
         <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4794,7 +4803,7 @@
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4826,7 +4835,7 @@
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4858,7 +4867,7 @@
         <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4922,7 +4931,7 @@
         <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -4954,13 +4963,13 @@
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>48</v>
@@ -4986,7 +4995,7 @@
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>172</v>
@@ -5018,7 +5027,7 @@
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>174</v>
@@ -5082,7 +5091,7 @@
         <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>178</v>
@@ -5114,7 +5123,7 @@
         <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>180</v>
@@ -5242,7 +5251,7 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>188</v>
@@ -5274,7 +5283,7 @@
         <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>190</v>
@@ -5434,7 +5443,7 @@
         <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>200</v>
@@ -5498,7 +5507,7 @@
         <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>204</v>
@@ -5562,7 +5571,7 @@
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>208</v>
@@ -5594,7 +5603,7 @@
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>210</v>
@@ -5626,7 +5635,7 @@
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>212</v>
@@ -5658,7 +5667,7 @@
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>214</v>
@@ -5690,7 +5699,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>216</v>
@@ -5722,7 +5731,7 @@
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>218</v>
@@ -5786,7 +5795,7 @@
         <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>222</v>
@@ -5818,7 +5827,7 @@
         <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>224</v>
@@ -5850,7 +5859,7 @@
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>226</v>
@@ -5882,7 +5891,7 @@
         <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>228</v>
@@ -5946,7 +5955,7 @@
         <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>232</v>
@@ -6074,7 +6083,7 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>240</v>
@@ -6266,7 +6275,7 @@
         <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>252</v>
@@ -6298,7 +6307,7 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>254</v>
@@ -6330,7 +6339,7 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>256</v>
@@ -6391,10 +6400,10 @@
         <v>2019</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>260</v>
@@ -6423,10 +6432,10 @@
         <v>2019</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>262</v>
@@ -6458,7 +6467,7 @@
         <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>264</v>
@@ -6490,7 +6499,7 @@
         <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>266</v>
@@ -6554,7 +6563,7 @@
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>270</v>
@@ -6586,7 +6595,7 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>272</v>
@@ -6650,7 +6659,7 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>276</v>
@@ -6682,7 +6691,7 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>278</v>
@@ -6714,7 +6723,7 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>280</v>
@@ -6810,7 +6819,7 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>286</v>
@@ -6842,7 +6851,7 @@
         <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>288</v>
@@ -6874,7 +6883,7 @@
         <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>290</v>
@@ -7034,7 +7043,7 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>300</v>
@@ -7066,7 +7075,7 @@
         <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>302</v>
@@ -7287,10 +7296,10 @@
         <v>2019</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>316</v>
@@ -7319,10 +7328,10 @@
         <v>2019</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>318</v>
@@ -7354,7 +7363,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>320</v>
@@ -7418,7 +7427,7 @@
         <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>324</v>
@@ -7482,7 +7491,7 @@
         <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>328</v>
@@ -7578,7 +7587,7 @@
         <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>334</v>
@@ -7610,7 +7619,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>336</v>
@@ -7642,7 +7651,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>338</v>
@@ -7770,7 +7779,7 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>346</v>
@@ -7802,7 +7811,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>348</v>
@@ -7834,7 +7843,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>350</v>
@@ -7866,7 +7875,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>352</v>
@@ -8026,7 +8035,7 @@
         <v>7</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>362</v>
@@ -8122,7 +8131,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>368</v>
@@ -8186,7 +8195,7 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>372</v>
@@ -8282,7 +8291,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>378</v>
@@ -8314,7 +8323,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>380</v>
@@ -8346,7 +8355,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>382</v>
@@ -8378,7 +8387,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>384</v>
@@ -8410,7 +8419,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>386</v>
@@ -8442,7 +8451,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>388</v>
@@ -8474,7 +8483,7 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>390</v>
@@ -11031,10 +11040,10 @@
         <v>2019</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>560</v>
@@ -11063,10 +11072,10 @@
         <v>2019</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>562</v>
@@ -13191,23 +13200,23 @@
         <v>699</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -13222,28 +13231,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13252,7 +13261,7 @@
         <v>2019</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:57</t>
+    <t xml:space="preserve">2026-09-07 13:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2019.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:11</t>
+    <t xml:space="preserve">2026-09-08 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
